--- a/Docs/03_test/テストケース.xlsx
+++ b/Docs/03_test/テストケース.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7933E795-5FAC-459C-A14F-EB18EF618641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC42152-A948-4896-BDFB-29133C7FFFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D329A028-469E-42D7-B307-ABD95E7B50B8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{D329A028-469E-42D7-B307-ABD95E7B50B8}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="トップページ" sheetId="1" r:id="rId1"/>
+    <sheet name="社員情報ページ" sheetId="2" r:id="rId2"/>
+    <sheet name="社員登録ページ" sheetId="3" r:id="rId3"/>
+    <sheet name="部門登録ページ" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,6 +41,497 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="45">
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト対象</t>
+    <rPh sb="3" eb="5">
+      <t>タイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>内容</t>
+    <rPh sb="0" eb="2">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手順</t>
+    <rPh sb="0" eb="2">
+      <t>テジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期待結果</t>
+    <rPh sb="0" eb="2">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>結果</t>
+    <rPh sb="0" eb="2">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員情報ボタン</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面遷移</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボタンを押す</t>
+    <rPh sb="4" eb="5">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員情報ページに遷移</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門情報ボタン</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面遷移</t>
+    <rPh sb="0" eb="4">
+      <t>ガメンセンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門情報ページに遷移</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員一覧表示ボタン</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員一覧を表示する</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員登録ボタン</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面表示</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員登録ページに遷移する</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字数チェック</t>
+    <rPh sb="0" eb="3">
+      <t>モジスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空チェック</t>
+    <rPh sb="0" eb="1">
+      <t>カラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何も入力しないで登録ボタンを押す</t>
+    <rPh sb="0" eb="1">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員名フィールド</t>
+    <rPh sb="0" eb="3">
+      <t>シャインメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「社員名は必須です」と表示される</t>
+    <rPh sb="1" eb="4">
+      <t>シャインメイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1文字入力してボタンを押す</t>
+    <rPh sb="1" eb="3">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「社員名は2～20文字で入力してください」と表示される</t>
+    <rPh sb="1" eb="4">
+      <t>シャインメイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>21文字入力してボタンを押す</t>
+    <rPh sb="2" eb="4">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>20文字入力してボタンを押す</t>
+    <rPh sb="2" eb="4">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2文字入力してボタンを押す</t>
+    <rPh sb="1" eb="3">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確認ページに遷移する</t>
+    <rPh sb="0" eb="2">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>境界値</t>
+    <rPh sb="0" eb="3">
+      <t>キョウカイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>性別選択</t>
+    <rPh sb="0" eb="2">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未選択チェック</t>
+    <rPh sb="0" eb="3">
+      <t>ミセンタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未選択のまま登録ボタンを押す</t>
+    <rPh sb="0" eb="3">
+      <t>ミセンタク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「性別は必須です」と表示される</t>
+    <rPh sb="1" eb="3">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「男性」を選択してボタンを押す</t>
+    <rPh sb="1" eb="3">
+      <t>ダンセイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「女性」を選択してボタンを押す</t>
+    <rPh sb="1" eb="3">
+      <t>ジョセイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門選択</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門を選択してボタンを押す</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門名フィールド</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勤務地選択</t>
+    <rPh sb="0" eb="3">
+      <t>キンムチ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「部門名は必須です」と表示される</t>
+    <rPh sb="1" eb="3">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「部門名は2～20文字で入力してください」と表示される</t>
+    <rPh sb="1" eb="3">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「勤務地は必須です」と表示される</t>
+    <rPh sb="1" eb="4">
+      <t>キンムチ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「東京」を選択してボタンを押す</t>
+    <rPh sb="1" eb="3">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
@@ -57,20 +551,41 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -79,8 +594,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -417,9 +938,564 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025B438D-C19E-436E-A140-F3F23FC7AE5C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="15.5" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="12.5" customWidth="1"/>
+    <col min="5" max="5" width="35.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C95D790E-9F9C-4F71-A5A6-5BC430326558}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="25.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA649D88-8B7F-4644-9F75-DF1A53898273}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1"/>
+    <col min="4" max="4" width="29.9140625" customWidth="1"/>
+    <col min="5" max="5" width="48.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02C195BA-1A5D-4B4E-9CC7-71238674F438}">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1"/>
+    <col min="4" max="4" width="29.9140625" customWidth="1"/>
+    <col min="5" max="5" width="48.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/03_test/テストケース.xlsx
+++ b/Docs/03_test/テストケース.xlsx
@@ -8,15 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC42152-A948-4896-BDFB-29133C7FFFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC0ACC2-3FBF-41F9-BE21-1914F522C43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{D329A028-469E-42D7-B307-ABD95E7B50B8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{D329A028-469E-42D7-B307-ABD95E7B50B8}"/>
   </bookViews>
   <sheets>
     <sheet name="トップページ" sheetId="1" r:id="rId1"/>
-    <sheet name="社員情報ページ" sheetId="2" r:id="rId2"/>
+    <sheet name="社員管理メニュー" sheetId="2" r:id="rId2"/>
     <sheet name="社員登録ページ" sheetId="3" r:id="rId3"/>
-    <sheet name="部門登録ページ" sheetId="4" r:id="rId4"/>
+    <sheet name="社員登録確認ページ" sheetId="5" r:id="rId4"/>
+    <sheet name="社員登録完了ページ" sheetId="6" r:id="rId5"/>
+    <sheet name="社員一覧表示ページ" sheetId="9" r:id="rId6"/>
+    <sheet name="部門登録ページ" sheetId="4" r:id="rId7"/>
+    <sheet name="部門登録確認ページ" sheetId="7" r:id="rId8"/>
+    <sheet name="部門登録完了ページ" sheetId="8" r:id="rId9"/>
+    <sheet name="部門一覧表示ページ" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="74">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -93,12 +99,328 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社員情報ボタン</t>
+    <t>画面遷移</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボタンを押す</t>
+    <rPh sb="4" eb="5">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面遷移</t>
+    <rPh sb="0" eb="4">
+      <t>ガメンセンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員一覧表示ボタン</t>
     <rPh sb="0" eb="2">
       <t>シャイン</t>
     </rPh>
     <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員登録ボタン</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員登録ページに遷移する</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字数チェック</t>
+    <rPh sb="0" eb="3">
+      <t>モジスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空チェック</t>
+    <rPh sb="0" eb="1">
+      <t>カラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員名フィールド</t>
+    <rPh sb="0" eb="3">
+      <t>シャインメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「社員名は2～20文字で入力してください」と表示される</t>
+    <rPh sb="1" eb="4">
+      <t>シャインメイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>確認ページに遷移する</t>
+    <rPh sb="0" eb="2">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>性別選択</t>
+    <rPh sb="0" eb="2">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未選択チェック</t>
+    <rPh sb="0" eb="3">
+      <t>ミセンタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門選択</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門名フィールド</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勤務地選択</t>
+    <rPh sb="0" eb="3">
+      <t>キンムチ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「部門名は必須です」と表示される</t>
+    <rPh sb="1" eb="3">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「部門名は2～20文字で入力してください」と表示される</t>
+    <rPh sb="1" eb="3">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戻るボタン</t>
+    <rPh sb="0" eb="1">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トップページに遷移する</t>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トップに戻るボタン</t>
+    <rPh sb="4" eb="5">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員情報ページに遷移する</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
       <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了ボタン</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了ページに遷移する</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録ページに遷移する</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>続けて登録するボタン</t>
+    <rPh sb="0" eb="1">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（境界値）</t>
+    <rPh sb="1" eb="4">
+      <t>キョウカイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門情報ページに遷移する</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員管理ボタン</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門管理ボタン</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員管理ページに遷移</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門管理ページに遷移</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -107,426 +429,403 @@
     <rPh sb="0" eb="2">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="2" eb="4">
-      <t>センイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ボタンを押す</t>
-    <rPh sb="4" eb="5">
-      <t>オ</t>
+    <t>一覧表示ページに遷移する</t>
+    <rPh sb="0" eb="4">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社員情報ページに遷移</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>センイ</t>
+    <t>「勤務地は入力必須です」と表示される</t>
+    <rPh sb="1" eb="4">
+      <t>キンムチ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門情報ボタン</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
+    <t>「性別は入力必須です」と表示される</t>
+    <rPh sb="1" eb="3">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>画面遷移</t>
-    <rPh sb="0" eb="4">
-      <t>ガメンセンイ</t>
+    <t>「社員名は入力必須です」と表示される</t>
+    <rPh sb="1" eb="4">
+      <t>シャインメイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門情報ページに遷移</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>センイ</t>
+    <t>表</t>
+    <rPh sb="0" eb="1">
+      <t>ヒョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社員一覧表示ボタン</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヒョウジ</t>
+    <t>データ一致</t>
+    <rPh sb="3" eb="5">
+      <t>イッチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社員一覧を表示する</t>
-    <rPh sb="0" eb="2">
+    <t>「社員管理メニューに戻る」ボタン</t>
+    <rPh sb="1" eb="3">
       <t>シャイン</t>
     </rPh>
-    <rPh sb="2" eb="4">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヒョウジ</t>
+    <rPh sb="3" eb="5">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>モド</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社員登録ボタン</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>トウロク</t>
+    <t>「トップページに戻る」ボタン</t>
+    <rPh sb="8" eb="9">
+      <t>モド</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>画面表示</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヒョウジ</t>
-    </rPh>
+    <t>(a)</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社員登録ページに遷移する</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>センイ</t>
-    </rPh>
+    <t>表示内容がpgAdminで「SELECT * FROM employee」の出力結果(a)と一致する</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>文字数チェック</t>
-    <rPh sb="0" eb="3">
-      <t>モジスウ</t>
-    </rPh>
+    <t>表示内容がpgAdminで「SELECT * FROM department」の出力結果(a)と一致する</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>空チェック</t>
-    <rPh sb="0" eb="1">
-      <t>カラ</t>
-    </rPh>
+    <t>→</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>何も入力しないで登録ボタンを押す</t>
-    <rPh sb="0" eb="1">
-      <t>ナニ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
+    <t>登録ボタン</t>
+    <rPh sb="0" eb="2">
       <t>トウロク</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社員名フィールド</t>
-    <rPh sb="0" eb="3">
-      <t>シャインメイ</t>
+    <t>「（何も入力しない）,未選択,男性」で完了ボタンを押す</t>
+    <rPh sb="15" eb="16">
+      <t>オトコ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「社員名は必須です」と表示される</t>
-    <rPh sb="1" eb="4">
-      <t>シャインメイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ヒョウジ</t>
+    <t>「フシギダネヒトカゲゼニガメピカチュウピッピ,未選択,男性」で完了ボタンを押す</t>
+    <rPh sb="31" eb="33">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>1文字入力してボタンを押す</t>
-    <rPh sb="1" eb="3">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="11" eb="12">
+    <t>「森鴎外,未選択,男性」で完了ボタンを押す</t>
+    <rPh sb="1" eb="4">
+      <t>モリオウガイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「社員名は2～20文字で入力してください」と表示される</t>
-    <rPh sb="1" eb="4">
-      <t>シャインメイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ヒョウジ</t>
+    <t>「カビゴンルカリオイーブイミュウツープリン,未選択,男性」で完了ボタンを押す</t>
+    <rPh sb="30" eb="32">
+      <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>21文字入力してボタンを押す</t>
-    <rPh sb="2" eb="4">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="12" eb="13">
+    <t>「森鷗外,未選択,未選択」で完了ボタンを押す</t>
+    <rPh sb="1" eb="5">
+      <t>モリオウガイ､</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ミセンタク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>20文字入力してボタンを押す</t>
-    <rPh sb="2" eb="4">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="12" eb="13">
+    <t>「与謝野晶子,未選択,女性」で完了ボタンを押す</t>
+    <rPh sb="1" eb="6">
+      <t>ヨサノアキコ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ミセンタク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>2文字入力してボタンを押す</t>
-    <rPh sb="1" eb="3">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="11" eb="12">
+    <t>「森鷗外,開発,男性」で完了ボタンを押す</t>
+    <rPh sb="1" eb="4">
+      <t>モリオウガイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>確認ページに遷移する</t>
-    <rPh sb="0" eb="2">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>センイ</t>
+    <t>「企画,未選択」で完了ボタンを押す</t>
+    <rPh sb="1" eb="3">
+      <t>キカク</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ミセンタク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>境界値</t>
-    <rPh sb="0" eb="3">
-      <t>キョウカイチ</t>
+    <t>「（何も入力しない）,東京」で完了ボタンを押す</t>
+    <rPh sb="2" eb="3">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>性別選択</t>
-    <rPh sb="0" eb="2">
-      <t>セイベツ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>センタク</t>
+    <t>「あ,東京」で完了ボタンを押す</t>
+    <rPh sb="3" eb="5">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>未選択チェック</t>
-    <rPh sb="0" eb="3">
-      <t>ミセンタク</t>
+    <t>「フシギダネヒトカゲゼニガメピカチュウピッピ,東京」で完了ボタンを押す</t>
+    <rPh sb="23" eb="25">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>未選択のまま登録ボタンを押す</t>
-    <rPh sb="0" eb="3">
-      <t>ミセンタク</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="12" eb="13">
+    <t>「企画,東京」で完了ボタンを押す</t>
+    <rPh sb="1" eb="3">
+      <t>キカク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「性別は必須です」と表示される</t>
-    <rPh sb="1" eb="3">
-      <t>セイベツ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
+    <t>「カビゴンルカリオイーブイミュウツープリン,東京」で完了ボタンを押す</t>
+    <rPh sb="22" eb="24">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「男性」を選択してボタンを押す</t>
+    <t>「企画,大阪」で完了ボタンを押す</t>
     <rPh sb="1" eb="3">
-      <t>ダンセイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="13" eb="14">
+      <t>キカク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>オオサカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「女性」を選択してボタンを押す</t>
-    <rPh sb="1" eb="3">
-      <t>ジョセイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>オ</t>
+    <t>「トップに戻る」ボタン</t>
+    <rPh sb="5" eb="6">
+      <t>モド</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門選択</t>
-    <rPh sb="0" eb="2">
+    <t>「部門情報ページに戻る」ボタン</t>
+    <rPh sb="1" eb="3">
       <t>ブモン</t>
     </rPh>
-    <rPh sb="2" eb="4">
-      <t>センタク</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>モド</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門を選択してボタンを押す</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>オ</t>
+    <t>部門情報ページに遷移する</t>
+    <rPh sb="0" eb="4">
+      <t>ブモンジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門名フィールド</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ナ</t>
+    <t>「あ,未選択,男性」で完了ボタンを押す</t>
+    <rPh sb="3" eb="6">
+      <t>ミセンタク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>勤務地選択</t>
+    <t>部門名が20文字までしか入力できないことを確認する</t>
     <rPh sb="0" eb="3">
-      <t>キンムチ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>センタク</t>
+      <t>ブモンメイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カクニン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「部門名は必須です」と表示される</t>
-    <rPh sb="1" eb="3">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="3" eb="4">
+    <t>社員名が20文字までしか入力できないことを確認する</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
       <t>メイ</t>
     </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ヒョウジ</t>
+    <rPh sb="6" eb="8">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カクニン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「部門名は2～20文字で入力してください」と表示される</t>
-    <rPh sb="1" eb="3">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「勤務地は必須です」と表示される</t>
-    <rPh sb="1" eb="4">
-      <t>キンムチ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「東京」を選択してボタンを押す</t>
-    <rPh sb="1" eb="3">
-      <t>トウキョウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>オ</t>
-    </rPh>
+    <t>○</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -534,7 +833,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -550,8 +849,14 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -561,6 +866,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -594,7 +917,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -602,6 +925,39 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -619,6 +975,3004 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>44450</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>61694</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>146459</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27458DFF-87E0-1F00-991A-5C0C9EA34796}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="704850" y="1204694"/>
+          <a:ext cx="3073400" cy="1227765"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>120651</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>90452</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>181449</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93BDB8E7-01A5-CE29-633B-322FB758FA72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5391151" y="1233452"/>
+          <a:ext cx="2260599" cy="1233997"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>918234</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{370DCFEA-4F32-1C0D-2602-17244390BDF3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="717551" y="2838451"/>
+          <a:ext cx="2956583" cy="1181099"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>99194</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>349250</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>117829</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{692BD05C-C60D-919B-E5A3-1A47DFC7E403}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5403850" y="2842394"/>
+          <a:ext cx="2197100" cy="1161635"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>241301</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>12701</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>664687</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4982E3C-115C-76ED-7EC7-37F6CC758F25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="241301" y="1803401"/>
+          <a:ext cx="3230086" cy="2863849"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>730249</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2183430</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>177799</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E568066A-E5A4-16E6-2A72-9322F430B228}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3714749" y="1809750"/>
+          <a:ext cx="2361231" cy="1987549"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>90166</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2027423</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>152982</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEF41850-7939-D6AC-51FC-A294B74958CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="838200" y="5081266"/>
+          <a:ext cx="5761223" cy="1891616"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1919473</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>139016</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34905783-1C4B-454A-B62F-28466174FB58}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="730250" y="7353300"/>
+          <a:ext cx="5761223" cy="1891616"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1900423</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>145366</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BFA26B1-C3D0-4606-B1D5-F4B5BDFA1693}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="711200" y="9645650"/>
+          <a:ext cx="5761223" cy="1891616"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>622173</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>200294</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>448346</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC3F60C9-CBE5-48E6-7CE5-F3D8BCD515ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7715123" y="7477394"/>
+          <a:ext cx="3128173" cy="1653906"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>41279</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>347100</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>140109</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3ED646ED-0DEB-88C5-6C29-B5288D4E8F2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7721600" y="5260979"/>
+          <a:ext cx="3680850" cy="1470430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>76201</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>145040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>984250</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>111600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94338622-0507-58F7-8A95-61ADF7165487}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="736601" y="1516640"/>
+          <a:ext cx="2870199" cy="1566760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>78057</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>506624</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>165848</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA9D55AE-26B7-2009-5614-64CFAD210211}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4572000" y="1221057"/>
+          <a:ext cx="5694574" cy="2373791"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1079499</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>176110</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DA1B061-7063-48FE-AF6A-90E86EFCFDE0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="831850" y="4324350"/>
+          <a:ext cx="2870199" cy="1566760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>190501</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>723901</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>92250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{728AEB6B-086B-4750-89DB-4C0755037361}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="850901" y="6502400"/>
+          <a:ext cx="2495550" cy="1362250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>463549</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>387350</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>121285</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5EA82EE-CBF3-1816-ECDF-21B7F3D26437}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4292599" y="4038600"/>
+          <a:ext cx="2552701" cy="2026285"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>181826</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>35455</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEF80B2A-759A-944D-004F-14DA994484C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4203700" y="6582626"/>
+          <a:ext cx="3067050" cy="1225229"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1458243</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>13351</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7056EF0-A84C-5B1B-71CA-5C6F83D50961}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="755650" y="3314700"/>
+          <a:ext cx="2652043" cy="2191401"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>768350</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>87920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1441450</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>13101</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC455436-9A41-535C-EA52-F03234E0ECE0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1428750" y="6037870"/>
+          <a:ext cx="3530600" cy="1525381"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>660401</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>146338</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1339850</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>98817</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{025FE121-76AC-C191-A446-CDA201072900}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1320801" y="8153688"/>
+          <a:ext cx="3536949" cy="1552679"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>514351</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>961327</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>133959</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CB44F79-D536-FC43-6B07-1411BCF84D97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174751" y="10185400"/>
+          <a:ext cx="3304476" cy="2985109"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>520701</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>114608</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1054101</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>121022</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E145C3A0-11D8-F059-3C49-99E1059A070B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1181101" y="13608358"/>
+          <a:ext cx="3390900" cy="1378014"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1048796</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>108333</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7B70077-DC69-02AC-CE5D-976CA9EA16A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1263650" y="15417800"/>
+          <a:ext cx="3303046" cy="1384683"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>181469</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1149350</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>89553</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3CC0D48-106B-405E-BCC0-CE15D3125C3E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="793750" y="17332819"/>
+          <a:ext cx="2305050" cy="1965484"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>431800</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>32974</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3728319</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>3650</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BE6C129-8863-8D1A-87A5-C1296C81213A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3949700" y="17412924"/>
+          <a:ext cx="3296519" cy="1799476"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>120650</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1136650</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>79534</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{648157B1-1797-4334-851C-45EC74519829}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="781050" y="19837400"/>
+          <a:ext cx="2305050" cy="1965484"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>806450</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>218297</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1375800</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>6759</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC326934-277F-492B-EF82-14ADA797D136}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4324350" y="19884247"/>
+          <a:ext cx="4620650" cy="1845862"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>120650</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1431134</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>67687</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9C2AD2E-7728-49EA-9755-B6104A5E873A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="781050" y="6057900"/>
+          <a:ext cx="2599534" cy="3160137"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>182484</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1429166</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAE17146-5B8D-5B2D-9DA5-EDB01F81B427}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="842884" y="9715500"/>
+          <a:ext cx="2535732" cy="2755900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>181844</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1803400</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>159151</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD909B31-C911-E6C3-29C1-AE578E9C27ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="933450" y="1324844"/>
+          <a:ext cx="3651250" cy="1577507"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>146050</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1676400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>205907</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CF85A62-5679-4124-9C14-07484A7EF7A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="806450" y="4343400"/>
+          <a:ext cx="3651250" cy="1577507"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>850901</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>418305</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>178459</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21E1D260-8169-16DC-8810-2F02FDE4DF53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5759451" y="977900"/>
+          <a:ext cx="2507454" cy="2400959"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>790193</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>167502</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>461310</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14F29CA5-555C-1599-ACF3-55771F924090}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5698743" y="3825102"/>
+          <a:ext cx="3931967" cy="2645548"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>182452</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1073150</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>111753</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E742247-FBAB-6FBB-E9DA-D9375457E72F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1104900" y="1096852"/>
+          <a:ext cx="2952750" cy="1986701"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>84807</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B6797C5-345D-5A71-6AE5-FEF9AE9F2344}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5213350" y="1227807"/>
+          <a:ext cx="4349750" cy="1737643"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>933450</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>151551</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{578C1BCA-FE11-4F89-9001-CC672F0F8833}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="965200" y="3879850"/>
+          <a:ext cx="2952750" cy="1986701"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>488950</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>166166</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>99192</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>57803</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF1EC3AA-8924-B516-8C1D-7E9859094861}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5403850" y="3595166"/>
+          <a:ext cx="3090042" cy="2634837"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>157816</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>95732</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>565286</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>53473</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82FFCA2E-0429-8405-A937-32DBB18EF820}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="157816" y="1880416"/>
+          <a:ext cx="4277628" cy="3821215"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>608263</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>86895</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2486543</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>200527</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{593BC71B-69AB-118F-92B5-448B4FAD2A3C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4478421" y="1871579"/>
+          <a:ext cx="2787333" cy="2613527"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>538382</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>82380</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1512779</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>167420</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17430B5A-A3B8-5327-63CD-E307EB268DFC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1197195" y="6257755"/>
+          <a:ext cx="5086022" cy="2156728"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>531813</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>47626</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1506210</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>132667</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FFFF540-94C8-44F5-84D1-F42069203B69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1190626" y="8755064"/>
+          <a:ext cx="5086022" cy="2156728"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>373062</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>87312</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1347459</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>172352</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07FEE60B-47D9-48D6-B207-04735E24F3AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1031875" y="11326812"/>
+          <a:ext cx="5086022" cy="2156728"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>309562</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>288363</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>159000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D762296-71F2-6EF9-9AAF-FAC03C965D59}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7604125" y="6342062"/>
+          <a:ext cx="4590488" cy="1833813"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>39687</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>111533</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>154280</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1618402-277C-6CFC-4766-4791EA390B46}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7993062" y="8818971"/>
+          <a:ext cx="3873501" cy="2114434"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>857251</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>100395</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>996950</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>124405</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5F5492C-A43A-A284-635D-B7022FFD8B51}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1517651" y="3072195"/>
+          <a:ext cx="2997199" cy="2310010"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>774700</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2436717</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0387D0D9-A05D-0FCD-1D72-C63D932AA76D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4292600" y="5848350"/>
+          <a:ext cx="4913217" cy="1809750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>374651</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>59779</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>977901</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>172027</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2F11487-B551-9AEB-C466-8D7E1E091E28}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1035051" y="8060779"/>
+          <a:ext cx="3460750" cy="2855448"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>501650</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>159469</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1885950</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>111453</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7ACBAFE5-354F-BCE2-166C-B42E83BCEAD5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1162050" y="11360869"/>
+          <a:ext cx="4241800" cy="1552184"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>241131</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>140259</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>958850</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>105570</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E511F66-2550-A81B-F7D5-F88EF56C9A54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="901531" y="5855259"/>
+          <a:ext cx="2006769" cy="1794111"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>112056</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1494815</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAB0CE18-BC42-3AFC-7162-5774ED165795}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="772456" y="5797550"/>
+          <a:ext cx="2671809" cy="2800350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>24504</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1486777</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70B42749-A7A1-3140-A2DA-EC6CD3C3D386}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684904" y="9029700"/>
+          <a:ext cx="2751323" cy="2698750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>330201</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>438491</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>102419</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EE55235-D127-E1D7-1025-C9C9882445C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="990601" y="14566900"/>
+          <a:ext cx="2965790" cy="2909119"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1885950</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>157886</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3515918</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>146550</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{232CFC0B-970A-360B-E8EF-17B980C27A81}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5403850" y="15016886"/>
+          <a:ext cx="4881168" cy="2046064"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>184151</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>43336</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>717550</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>98932</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECCCFFFE-6F5E-6F5A-2631-4FD4A665D9DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="844551" y="1414936"/>
+          <a:ext cx="3676649" cy="1655796"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>423281</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>312324</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>127779</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C7B2167-585F-BC93-08EE-954A44D2CBE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5820781" y="1212850"/>
+          <a:ext cx="3191043" cy="2115329"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>717549</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>125446</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEA58DED-D6A8-42C0-B54D-19EE9B061767}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="844550" y="4184650"/>
+          <a:ext cx="3676649" cy="1655796"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>342901</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>172161</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>118282</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCC01FBC-2E04-BE07-5B41-C55C9D284C64}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5740401" y="3530600"/>
+          <a:ext cx="3131260" cy="2988482"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>308143</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>32529</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6442025B-0D51-4372-8824-FC3211C52C78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="933450" y="1117600"/>
+          <a:ext cx="3191043" cy="2115329"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>257343</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>140479</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B43F77-C515-4FF4-8E18-C74CA1697FCC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="882650" y="3740150"/>
+          <a:ext cx="3191043" cy="2115329"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>107951</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>80746</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>311150</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>89699</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC038B73-B04F-450C-4D23-CCA1F78D1D9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6261101" y="995146"/>
+          <a:ext cx="2184399" cy="2294953"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1333500</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>182023</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>42372</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEBC2334-9BAA-0D3E-2217-C3D1C2546FD8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5149850" y="3839623"/>
+          <a:ext cx="4800600" cy="1917749"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -938,13 +4292,236 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025B438D-C19E-436E-A140-F3F23FC7AE5C}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
-    <col min="5" max="5" width="35.25" customWidth="1"/>
+    <col min="5" max="5" width="20.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="7">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="7">
+        <v>2</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E985560-6883-433C-8F85-EB04AFD20175}">
+  <dimension ref="A1:L49"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="28.1640625" customWidth="1"/>
+    <col min="3" max="3" width="11.25" customWidth="1"/>
+    <col min="4" max="4" width="11.9140625" customWidth="1"/>
+    <col min="5" max="5" width="33.08203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -975,18 +4552,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -994,29 +4573,467 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="7">
+        <v>1</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="7">
+        <v>2</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="7">
+        <v>3</v>
+      </c>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C95D790E-9F9C-4F71-A5A6-5BC430326558}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="17.08203125" customWidth="1"/>
@@ -1024,7 +5041,7 @@
     <col min="5" max="5" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1047,58 +5064,410 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="7">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="7">
+        <v>2</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="7">
+        <v>3</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA649D88-8B7F-4644-9F75-DF1A53898273}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.9140625" customWidth="1"/>
     <col min="3" max="3" width="20.58203125" customWidth="1"/>
-    <col min="4" max="4" width="29.9140625" customWidth="1"/>
+    <col min="4" max="4" width="53.1640625" customWidth="1"/>
     <col min="5" max="5" width="48.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1130,18 +5499,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1149,37 +5520,41 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:7" ht="36.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1187,37 +5562,41 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1225,18 +5604,20 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1244,16 +5625,18 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1261,16 +5644,18 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1278,16 +5663,20 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1295,32 +5684,1907 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="D11" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G11" s="1"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="7">
+        <v>1</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="7">
+        <v>2</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="7">
+        <v>3</v>
+      </c>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="7"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="7"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="7"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="7">
+        <v>4</v>
+      </c>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="7"/>
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="7"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="7"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="7"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="7"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="7"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="7"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="7">
+        <v>5</v>
+      </c>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="7"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="7"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="7"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="7"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="7"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="7"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="7"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="7">
+        <v>6</v>
+      </c>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="7"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="7"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="7"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="7"/>
+      <c r="B78" s="7"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="7"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="7"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="7"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="7"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="7"/>
+      <c r="B82" s="7"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="7"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" s="7"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" s="7"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" s="7"/>
+      <c r="B85" s="7"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" s="7"/>
+      <c r="B86" s="7"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" s="7">
+        <v>7</v>
+      </c>
+      <c r="B88" s="7"/>
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" s="7"/>
+      <c r="B89" s="7"/>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" s="7"/>
+      <c r="B90" s="7"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="7"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" s="7"/>
+      <c r="B91" s="7"/>
+      <c r="C91" s="7"/>
+      <c r="D91" s="7"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" s="7"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" s="7"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" s="7"/>
+      <c r="B94" s="7"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="7"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" s="7">
+        <v>8</v>
+      </c>
+      <c r="B96" s="7"/>
+      <c r="C96" s="7"/>
+      <c r="D96" s="7"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" s="7"/>
+      <c r="B97" s="7"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" s="7"/>
+      <c r="B98" s="7"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="7"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" s="7"/>
+      <c r="B99" s="7"/>
+      <c r="C99" s="7"/>
+      <c r="D99" s="7"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" s="7"/>
+      <c r="B100" s="7"/>
+      <c r="C100" s="7"/>
+      <c r="D100" s="7"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" s="7"/>
+      <c r="B101" s="7"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" s="7"/>
+      <c r="B102" s="7"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="7"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" s="7">
+        <v>9</v>
+      </c>
+      <c r="B104" s="7"/>
+      <c r="C104" s="7"/>
+      <c r="D104" s="7"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" s="7"/>
+      <c r="B105" s="7"/>
+      <c r="C105" s="7"/>
+      <c r="D105" s="7"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" s="7"/>
+      <c r="B106" s="7"/>
+      <c r="C106" s="7"/>
+      <c r="D106" s="7"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" s="7"/>
+      <c r="B107" s="7"/>
+      <c r="C107" s="7"/>
+      <c r="D107" s="7"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" s="7"/>
+      <c r="B108" s="7"/>
+      <c r="C108" s="7"/>
+      <c r="D108" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" s="7"/>
+      <c r="B109" s="7"/>
+      <c r="C109" s="7"/>
+      <c r="D109" s="7"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" s="7"/>
+      <c r="B110" s="7"/>
+      <c r="C110" s="7"/>
+      <c r="D110" s="7"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" s="7"/>
+      <c r="B111" s="7"/>
+      <c r="C111" s="7"/>
+      <c r="D111" s="7"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" s="7"/>
+      <c r="B112" s="7"/>
+      <c r="C112" s="7"/>
+      <c r="D112" s="7"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" s="7"/>
+      <c r="B113" s="7"/>
+      <c r="C113" s="7"/>
+      <c r="D113" s="7"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" s="7">
+        <v>10</v>
+      </c>
+      <c r="B115" s="7"/>
+      <c r="C115" s="7"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="7"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" s="7"/>
+      <c r="B116" s="7"/>
+      <c r="C116" s="7"/>
+      <c r="D116" s="7"/>
+      <c r="E116" s="7"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" s="7"/>
+      <c r="B117" s="7"/>
+      <c r="C117" s="7"/>
+      <c r="D117" s="7"/>
+      <c r="E117" s="7"/>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" s="7"/>
+      <c r="B118" s="7"/>
+      <c r="C118" s="7"/>
+      <c r="D118" s="7"/>
+      <c r="E118" s="7"/>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" s="7"/>
+      <c r="B119" s="7"/>
+      <c r="C119" s="7"/>
+      <c r="D119" s="7"/>
+      <c r="E119" s="7"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" s="7"/>
+      <c r="B120" s="7"/>
+      <c r="C120" s="7"/>
+      <c r="D120" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E120" s="7"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A121" s="7"/>
+      <c r="B121" s="7"/>
+      <c r="C121" s="7"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" s="7"/>
+      <c r="B122" s="7"/>
+      <c r="C122" s="7"/>
+      <c r="D122" s="7"/>
+      <c r="E122" s="7"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A123" s="7"/>
+      <c r="B123" s="7"/>
+      <c r="C123" s="7"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="7"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A124" s="7"/>
+      <c r="B124" s="7"/>
+      <c r="C124" s="7"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02C195BA-1A5D-4B4E-9CC7-71238674F438}">
-  <dimension ref="A1:G9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E924555-BC9F-40A2-B4E2-737F8C4831B2}">
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.08203125" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="27.9140625" customWidth="1"/>
+    <col min="5" max="5" width="38.58203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="7">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="7">
+        <v>2</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DCBB6DA-E9B0-49D8-A214-56C5C10937ED}">
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="18.9140625" customWidth="1"/>
+    <col min="3" max="3" width="11.58203125" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" customWidth="1"/>
+    <col min="5" max="5" width="28.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="7">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="7">
+        <v>2</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F69357E3-E0A2-4D25-BC97-BBF6092490AA}">
+  <dimension ref="A1:M57"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="11.25" customWidth="1"/>
+    <col min="4" max="4" width="11.9140625" customWidth="1"/>
+    <col min="5" max="5" width="33.08203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="7">
+        <v>1</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="7">
+        <v>2</v>
+      </c>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="7"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="7"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
+      <c r="M43" s="7"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
+      <c r="M44" s="7"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
+      <c r="M45" s="7"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="7">
+        <v>3</v>
+      </c>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="7"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="7"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="7"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="7"/>
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="7"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02C195BA-1A5D-4B4E-9CC7-71238674F438}">
+  <dimension ref="A1:G98"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="16.9140625" customWidth="1"/>
     <col min="3" max="3" width="20.58203125" customWidth="1"/>
-    <col min="4" max="4" width="29.9140625" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" customWidth="1"/>
     <col min="5" max="5" width="48.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1352,18 +7616,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1371,37 +7637,41 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:7" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1409,37 +7679,41 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:7" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1447,18 +7721,20 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1466,16 +7742,18 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1483,20 +7761,1326 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="7">
+        <v>1</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="11"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="7">
+        <v>2</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="7">
+        <v>3</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="13"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="13"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="13"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="13"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="13"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="13"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="13"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="13"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="13"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="13"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="13"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="13"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="13"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="7">
+        <v>4</v>
+      </c>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="7"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="7"/>
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E56" s="7"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="7"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="7"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="7"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="7"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+    </row>
+    <row r="61" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="62" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="7">
+        <v>5</v>
+      </c>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+    </row>
+    <row r="63" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="7"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+    </row>
+    <row r="64" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="7"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+    </row>
+    <row r="65" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="7"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+    </row>
+    <row r="66" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="7"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+    </row>
+    <row r="67" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="7"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+    </row>
+    <row r="68" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="7"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+    </row>
+    <row r="69" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="7"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E69" s="7"/>
+    </row>
+    <row r="70" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="7"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+    </row>
+    <row r="71" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="7"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+    </row>
+    <row r="72" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="7"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+    </row>
+    <row r="73" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="7"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+    </row>
+    <row r="74" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="7"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+    </row>
+    <row r="75" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="7"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="7">
+        <v>6</v>
+      </c>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="7"/>
+      <c r="B78" s="7"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="7"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="7"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="7"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="7"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="7"/>
+      <c r="B82" s="7"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="7"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" s="7"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" s="7"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" s="7"/>
+      <c r="B85" s="7"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" s="7"/>
+      <c r="B86" s="7"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" s="7"/>
+      <c r="B87" s="7"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" s="7"/>
+      <c r="B88" s="7"/>
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" s="7"/>
+      <c r="B89" s="7"/>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" s="7">
+        <v>7</v>
+      </c>
+      <c r="B91" s="7"/>
+      <c r="C91" s="7"/>
+      <c r="D91" s="7"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" s="7"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" s="7"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" s="7"/>
+      <c r="B94" s="7"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="7"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" s="7"/>
+      <c r="B95" s="7"/>
+      <c r="C95" s="7"/>
+      <c r="D95" s="7"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" s="7"/>
+      <c r="B96" s="7"/>
+      <c r="C96" s="7"/>
+      <c r="D96" s="7"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" s="7"/>
+      <c r="B97" s="7"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" s="7"/>
+      <c r="B98" s="7"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C133C39A-04AE-4CDE-B5D8-CDF03E21BAE3}">
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="17.58203125" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="20.9140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="7">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="7">
+        <v>2</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0AFCC20-0D94-4918-8E04-2C07B5198F64}">
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="19.25" customWidth="1"/>
+    <col min="4" max="4" width="13.5" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="7">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="7">
+        <v>2</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>